--- a/main/ig/StructureDefinition-mesures-original-data.xlsx
+++ b/main/ig/StructureDefinition-mesures-original-data.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>3.1.0</t>
+    <t>3.1.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-29T14:02:34+00:00</t>
+    <t>2026-01-30T09:35:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-mesures-original-data.xlsx
+++ b/main/ig/StructureDefinition-mesures-original-data.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-30T09:35:57+00:00</t>
+    <t>2026-01-30T10:15:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-mesures-original-data.xlsx
+++ b/main/ig/StructureDefinition-mesures-original-data.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>3.1.1</t>
+    <t>3.2.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-30T10:15:26+00:00</t>
+    <t>2026-02-02T08:09:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-mesures-original-data.xlsx
+++ b/main/ig/StructureDefinition-mesures-original-data.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-02T08:09:27+00:00</t>
+    <t>2026-02-02T08:10:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-mesures-original-data.xlsx
+++ b/main/ig/StructureDefinition-mesures-original-data.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-02T08:10:43+00:00</t>
+    <t>2026-02-02T09:29:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-mesures-original-data.xlsx
+++ b/main/ig/StructureDefinition-mesures-original-data.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>3.2.0-ballot</t>
+    <t>3.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-02T09:29:40+00:00</t>
+    <t>2026-02-18T12:52:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-mesures-original-data.xlsx
+++ b/main/ig/StructureDefinition-mesures-original-data.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-18T12:52:41+00:00</t>
+    <t>2026-02-23T17:17:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -75,7 +75,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>FRANCE</t>
+    <t>France</t>
   </si>
   <si>
     <t>Description</t>

--- a/main/ig/StructureDefinition-mesures-original-data.xlsx
+++ b/main/ig/StructureDefinition-mesures-original-data.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-23T17:17:29+00:00</t>
+    <t>2026-03-18T17:41:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-mesures-original-data.xlsx
+++ b/main/ig/StructureDefinition-mesures-original-data.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-18T17:41:07+00:00</t>
+    <t>2026-03-31T09:00:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-mesures-original-data.xlsx
+++ b/main/ig/StructureDefinition-mesures-original-data.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-31T09:00:47+00:00</t>
+    <t>2026-05-06T11:42:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -75,7 +75,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>France</t>
+    <t>France (la)</t>
   </si>
   <si>
     <t>Description</t>

--- a/main/ig/StructureDefinition-mesures-original-data.xlsx
+++ b/main/ig/StructureDefinition-mesures-original-data.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-06T11:42:59+00:00</t>
+    <t>2026-05-07T07:18:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-mesures-original-data.xlsx
+++ b/main/ig/StructureDefinition-mesures-original-data.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-07T07:18:48+00:00</t>
+    <t>2026-05-07T07:24:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-mesures-original-data.xlsx
+++ b/main/ig/StructureDefinition-mesures-original-data.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-07T07:24:38+00:00</t>
+    <t>2026-06-09T08:46:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -257,7 +257,7 @@
 </t>
   </si>
   <si>
-    <t>Nombre de jours</t>
+    <t>Valeur originale de la donnée</t>
   </si>
   <si>
     <t xml:space="preserve">ele-1

--- a/main/ig/StructureDefinition-mesures-original-data.xlsx
+++ b/main/ig/StructureDefinition-mesures-original-data.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-09T08:46:34+00:00</t>
+    <t>2026-06-26T10:39:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
